--- a/ITI/MHD/StructureDefinition-IHE.MHD.FindDocumentReferencesResponseMessage.xlsx
+++ b/ITI/MHD/StructureDefinition-IHE.MHD.FindDocumentReferencesResponseMessage.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2933" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2932" uniqueCount="307">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>4.2.3</t>
+    <t>4.2.4</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-31T14:38:46-05:00</t>
+    <t>2026-06-15T14:55:16-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -879,23 +879,8 @@
     <t>Bundle.entry:DocumentReference.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">DocumentReference {https://profiles.ihe.net/ITI/MHD/StructureDefinition/IHE.MHD.Minimal.DocumentReference}
+    <t xml:space="preserve">DocumentReference
 </t>
-  </si>
-  <si>
-    <t>A reference to a document</t>
-  </si>
-  <si>
-    <t>A reference to a document of any kind for any purpose. Provides metadata about the document so that the document can be discovered and managed. The scope of a document is any seralized object with a mime-type, so includes formal patient centric documents (CDA), cliical notes, scanned paper, and non-patient specific documents like policy text.</t>
-  </si>
-  <si>
-    <t>Usually, this is used for documents other than those defined by FHIR.</t>
-  </si>
-  <si>
-    <t>Document[classCode="DOC" and moodCode="EVN"]</t>
-  </si>
-  <si>
-    <t>when describing a CDA</t>
   </si>
   <si>
     <t>Bundle.entry:DocumentReference.search</t>
@@ -1320,7 +1305,7 @@
     <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="93.5625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="17.46875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1346,7 +1331,7 @@
     <col min="34" max="34" width="8.859375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="22.43359375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="43.1796875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="20.3359375" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="37.16015625" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.45703125" customWidth="true" bestFit="true"/>
   </cols>
@@ -7502,20 +7487,18 @@
         <v>79</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K55" t="s" s="2">
         <v>275</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>276</v>
+        <v>195</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>278</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>79</v>
@@ -7582,10 +7565,10 @@
         <v>79</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>279</v>
+        <v>79</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>280</v>
+        <v>79</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>79</v>
@@ -7593,7 +7576,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="B56" t="s" s="2">
         <v>197</v>
@@ -7705,7 +7688,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="B57" t="s" s="2">
         <v>201</v>
@@ -7817,7 +7800,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="B58" t="s" s="2">
         <v>202</v>
@@ -7931,7 +7914,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="B59" t="s" s="2">
         <v>203</v>
@@ -8047,7 +8030,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="B60" t="s" s="2">
         <v>204</v>
@@ -8161,7 +8144,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="B61" t="s" s="2">
         <v>210</v>
@@ -8275,7 +8258,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="B62" t="s" s="2">
         <v>215</v>
@@ -8387,7 +8370,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="B63" t="s" s="2">
         <v>219</v>
@@ -8499,7 +8482,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="B64" t="s" s="2">
         <v>220</v>
@@ -8613,7 +8596,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="B65" t="s" s="2">
         <v>221</v>
@@ -8729,7 +8712,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="B66" t="s" s="2">
         <v>222</v>
@@ -8841,7 +8824,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="B67" t="s" s="2">
         <v>227</v>
@@ -8955,7 +8938,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="B68" t="s" s="2">
         <v>231</v>
@@ -9067,7 +9050,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="B69" t="s" s="2">
         <v>234</v>
@@ -9179,7 +9162,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="B70" t="s" s="2">
         <v>236</v>
@@ -9291,7 +9274,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B71" t="s" s="2">
         <v>239</v>
@@ -9403,7 +9386,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="B72" t="s" s="2">
         <v>242</v>
@@ -9515,7 +9498,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="B73" t="s" s="2">
         <v>246</v>
@@ -9627,7 +9610,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="B74" t="s" s="2">
         <v>247</v>
@@ -9741,7 +9724,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="B75" t="s" s="2">
         <v>248</v>
@@ -9857,7 +9840,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="B76" t="s" s="2">
         <v>249</v>
@@ -9969,7 +9952,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="B77" t="s" s="2">
         <v>252</v>
@@ -10081,7 +10064,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="B78" t="s" s="2">
         <v>255</v>
@@ -10195,7 +10178,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="B79" t="s" s="2">
         <v>259</v>
@@ -10309,7 +10292,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="B80" t="s" s="2">
         <v>263</v>
@@ -10423,10 +10406,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10449,19 +10432,19 @@
         <v>90</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>79</v>
@@ -10510,7 +10493,7 @@
         <v>79</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>

--- a/ITI/MHD/StructureDefinition-IHE.MHD.FindDocumentReferencesResponseMessage.xlsx
+++ b/ITI/MHD/StructureDefinition-IHE.MHD.FindDocumentReferencesResponseMessage.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>4.2.4</t>
+    <t>4.2.5-comment</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T14:55:16-05:00</t>
+    <t>2026-06-16T19:25:56-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
